--- a/output/pdf_financials_xlsx/ASL.xlsx
+++ b/output/pdf_financials_xlsx/ASL.xlsx
@@ -6036,49 +6036,49 @@
         <v>0.030105</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.376837</v>
+        <v>0.649118</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.833592</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.026592</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.026592</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.026592</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.026592</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.197592</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.091392</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.323592</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.410592</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.410592</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.780592</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.847592</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.847592</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.847592</v>
       </c>
     </row>
     <row r="93">
@@ -7631,16 +7631,16 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.41153</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.478814</v>
+        <v>-1.019033</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>2.54587</v>
+        <v>1.412777</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.077515</v>
+        <v>-0.027146</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -9970,7 +9970,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10360,7 +10364,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11217,7 +11225,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -12207,7 +12219,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -12819,7 +12835,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -13122,7 +13142,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -13934,7 +13958,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -15144,7 +15172,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -15843,7 +15875,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -16815,7 +16851,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -30800,7 +30840,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -32420,7 +32464,11 @@
           <t>Exploration and evaluation expenditures 10</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -34147,7 +34195,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ASL.xlsx
+++ b/output/pdf_financials_xlsx/ASL.xlsx
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000898</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000566</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.022712</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.009920999999999999</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1116,16 +1116,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.006411</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.002477</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.004211</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.017617</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -2093,19 +2093,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.046597</v>
+        <v>-0.047495</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.156912</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.043984</v>
+        <v>-1.04455</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.258195</v>
+        <v>-2.280907</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-4.094229</v>
+        <v>-4.10415</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.70818</v>
@@ -2120,16 +2120,16 @@
         <v>-0.341363</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.070406</v>
+        <v>0.063995</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.828724</v>
+        <v>-0.831201</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.714961</v>
+        <v>-1.719172</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.306897</v>
+        <v>-0.324514</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-0.375529</v>
@@ -2217,19 +2217,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.046597</v>
+        <v>-0.047495</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.156912</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.042682</v>
+        <v>-1.043248</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.243632</v>
+        <v>-2.266344</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4.072904</v>
+        <v>-4.082825</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.695462</v>
@@ -2244,16 +2244,16 @@
         <v>-0.341363</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.070406</v>
+        <v>0.063995</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.828724</v>
+        <v>-0.831201</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.70016</v>
+        <v>-1.704371</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.284021</v>
+        <v>-0.301638</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-0.371178</v>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.169244</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.018096</v>
@@ -2547,13 +2547,13 @@
         <v>0.179034</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.00562</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000409</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.00469</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.747698</v>
@@ -2571,16 +2571,16 @@
         <v>1.00499</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.75631</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.373511</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.204395</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.064997</v>
       </c>
     </row>
     <row r="35">
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.169244</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.018096</v>
@@ -2663,13 +2663,13 @@
         <v>0.179034</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.00562</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000409</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.00469</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.747698</v>
@@ -2687,16 +2687,16 @@
         <v>1.059678</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.214717</v>
+        <v>0.971027</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.182738</v>
+        <v>0.556249</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.012525</v>
+        <v>0.21692</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.064997</v>
       </c>
     </row>
     <row r="37">
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.169244</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.025</v>
@@ -3359,10 +3359,10 @@
         <v>0.075644</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.014723</v>
+        <v>0.009103</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.000409</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -3383,16 +3383,16 @@
         <v>0.007724</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.776875</v>
+        <v>0.020565</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.380094</v>
+        <v>0.006583</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.213863</v>
+        <v>0.009468000000000001</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.072283</v>
+        <v>0.007286</v>
       </c>
     </row>
     <row r="49">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11518,7 +11518,11 @@
           <t>Reclamation deposit (Note 15)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -13247,7 +13251,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -18380,7 +18384,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
@@ -21938,7 +21942,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -38949,7 +38957,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -41881,7 +41889,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -43160,7 +43168,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -45330,7 +45338,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -48475,7 +48483,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E398" s="5" t="n">

--- a/output/pdf_financials_xlsx/ASL.xlsx
+++ b/output/pdf_financials_xlsx/ASL.xlsx
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>0.236028</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>0.265887</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.039964</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.030105</v>
@@ -18792,7 +18792,11 @@
           <t>Share capital – Note 3</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
         <v>0.236028</v>
       </c>
@@ -18891,7 +18895,11 @@
           <t>Contributed surplus – Note 3</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
         <v>0.039964</v>
       </c>
